--- a/relatorios/contabilidade/RESUMO_3_LOJAS_AGOSTO_2026_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RESUMO_3_LOJAS_AGOSTO_2026_pgto_05-09-2026.xlsx
@@ -10,7 +10,7 @@
     <sheet name="RESUMO 3 LOJAS AGO.26" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RESUMO 3 LOJAS AGO.26'!$A$4:$O$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RESUMO 3 LOJAS AGO.26'!$A$4:$P$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00;-R$ #,##0.00;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,6 +66,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="000000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00000000"/>
       <sz val="9"/>
@@ -94,7 +99,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -119,6 +124,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -158,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -174,23 +184,24 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -558,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -572,10 +583,11 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="70" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="70" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -650,20 +662,25 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
           <t>VALE TRANSP. 6%</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>TOTAL DESCONTOS</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>LÍQUIDO PARCIAL</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO</t>
         </is>
@@ -689,6 +706,7 @@
       <c r="M5" s="5" t="n"/>
       <c r="N5" s="5" t="n"/>
       <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -720,22 +738,26 @@
       <c r="I6" s="7" t="n">
         <v>199</v>
       </c>
-      <c r="J6" s="8" t="n">
-        <v>5847.41</v>
+      <c r="J6" s="8">
+        <f>SUM(B6:I6)</f>
+        <v/>
       </c>
       <c r="K6" s="7" t="n">
         <v>-199</v>
       </c>
-      <c r="L6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>-199</v>
-      </c>
-      <c r="N6" s="9" t="n">
-        <v>5648.41</v>
-      </c>
-      <c r="O6" s="10" t="inlineStr">
+      <c r="L6" s="9" t="n"/>
+      <c r="M6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="8">
+        <f>SUM(K6:M6)</f>
+        <v/>
+      </c>
+      <c r="O6" s="10">
+        <f>J6+N6</f>
+        <v/>
+      </c>
+      <c r="P6" s="11" t="inlineStr">
         <is>
           <t>Não recebe comissão. Dia 15/08 trabalhado com folga compensatória.</t>
         </is>
@@ -771,22 +793,26 @@
       <c r="I7" s="7" t="n">
         <v>189</v>
       </c>
-      <c r="J7" s="8" t="n">
-        <v>5040.49</v>
+      <c r="J7" s="8">
+        <f>SUM(B7:I7)</f>
+        <v/>
       </c>
       <c r="K7" s="7" t="n">
         <v>-189</v>
       </c>
-      <c r="L7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>-189</v>
-      </c>
-      <c r="N7" s="9" t="n">
-        <v>4851.49</v>
-      </c>
-      <c r="O7" s="10" t="inlineStr">
+      <c r="L7" s="9" t="n"/>
+      <c r="M7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="8">
+        <f>SUM(K7:M7)</f>
+        <v/>
+      </c>
+      <c r="O7" s="10">
+        <f>J7+N7</f>
+        <v/>
+      </c>
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>Comissão fixa de R$ 2.000,00 (apurado R$ 909,51 + complemento R$ 1.090,49). 3 madrugadas = 24 h noturnas.</t>
         </is>
@@ -822,22 +848,26 @@
       <c r="I8" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="J8" s="8" t="n">
-        <v>3402.06</v>
+      <c r="J8" s="8">
+        <f>SUM(B8:I8)</f>
+        <v/>
       </c>
       <c r="K8" s="7" t="n">
         <v>-73</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="L8" s="9" t="n"/>
+      <c r="M8" s="7" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>-157.29</v>
-      </c>
-      <c r="N8" s="9" t="n">
-        <v>3244.77</v>
-      </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="N8" s="8">
+        <f>SUM(K8:M8)</f>
+        <v/>
+      </c>
+      <c r="O8" s="10">
+        <f>J8+N8</f>
+        <v/>
+      </c>
+      <c r="P8" s="11" t="inlineStr">
         <is>
           <t>24 horas extras. Adicional noturno fixo de R$ 350,00 — conferir com o ponto.</t>
         </is>
@@ -873,22 +903,26 @@
       <c r="I9" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="J9" s="8" t="n">
-        <v>145.18</v>
+      <c r="J9" s="8">
+        <f>SUM(B9:I9)</f>
+        <v/>
       </c>
       <c r="K9" s="7" t="n">
         <v>-22</v>
       </c>
-      <c r="L9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="8" t="n">
-        <v>-22</v>
-      </c>
-      <c r="N9" s="9" t="n">
-        <v>123.18</v>
-      </c>
-      <c r="O9" s="10" t="inlineStr">
+      <c r="L9" s="9" t="n"/>
+      <c r="M9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="8">
+        <f>SUM(K9:M9)</f>
+        <v/>
+      </c>
+      <c r="O9" s="10">
+        <f>J9+N9</f>
+        <v/>
+      </c>
+      <c r="P9" s="11" t="inlineStr">
         <is>
           <t>Férias de 01 a 31/08 pagas em recibo próprio (saiu em 04/08, volta em 04/09). Comissão dos dias 01 e 02/08.</t>
         </is>
@@ -924,22 +958,26 @@
       <c r="I10" s="7" t="n">
         <v>192</v>
       </c>
-      <c r="J10" s="8" t="n">
-        <v>3569.45</v>
+      <c r="J10" s="8">
+        <f>SUM(B10:I10)</f>
+        <v/>
       </c>
       <c r="K10" s="7" t="n">
         <v>-192</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="L10" s="9" t="n"/>
+      <c r="M10" s="7" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="M10" s="8" t="n">
-        <v>-276.29</v>
-      </c>
-      <c r="N10" s="9" t="n">
-        <v>3293.16</v>
-      </c>
-      <c r="O10" s="10" t="inlineStr">
+      <c r="N10" s="8">
+        <f>SUM(K10:M10)</f>
+        <v/>
+      </c>
+      <c r="O10" s="10">
+        <f>J10+N10</f>
+        <v/>
+      </c>
+      <c r="P10" s="11" t="inlineStr">
         <is>
           <t>Feriado 15/08 trabalhado. 2 madrugadas = 16 h noturnas, com folga no dia seguinte.</t>
         </is>
@@ -975,22 +1013,26 @@
       <c r="I11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="J11" s="8" t="n">
-        <v>2948.78</v>
+      <c r="J11" s="8">
+        <f>SUM(B11:I11)</f>
+        <v/>
       </c>
       <c r="K11" s="7" t="n">
         <v>-10</v>
       </c>
-      <c r="L11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>-10</v>
-      </c>
-      <c r="N11" s="9" t="n">
-        <v>2938.78</v>
-      </c>
-      <c r="O11" s="10" t="inlineStr">
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8">
+        <f>SUM(K11:M11)</f>
+        <v/>
+      </c>
+      <c r="O11" s="10">
+        <f>J11+N11</f>
+        <v/>
+      </c>
+      <c r="P11" s="11" t="inlineStr">
         <is>
           <t>Comissão do Arraial (R$ 368,78) + loja Centro (R$ 2,65). Feriado 15/08 trabalhado.</t>
         </is>
@@ -1026,22 +1068,26 @@
       <c r="I12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="8" t="n">
-        <v>1973.36</v>
+      <c r="J12" s="8">
+        <f>SUM(B12:I12)</f>
+        <v/>
       </c>
       <c r="K12" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="L12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="9" t="n">
-        <v>1973.36</v>
-      </c>
-      <c r="O12" s="10" t="inlineStr">
+      <c r="L12" s="9" t="n"/>
+      <c r="M12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="8">
+        <f>SUM(K12:M12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="10">
+        <f>J12+N12</f>
+        <v/>
+      </c>
+      <c r="P12" s="11" t="inlineStr">
         <is>
           <t>1º mês completo após a admissão. Feriado 15/08 trabalhado.</t>
         </is>
@@ -1077,86 +1123,94 @@
       <c r="I13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="8" t="n">
-        <v>2532.38</v>
+      <c r="J13" s="8">
+        <f>SUM(B13:I13)</f>
+        <v/>
       </c>
       <c r="K13" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="L13" s="9" t="n"/>
+      <c r="M13" s="7" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="M13" s="8" t="n">
-        <v>-84.29000000000001</v>
-      </c>
-      <c r="N13" s="9" t="n">
-        <v>2448.09</v>
-      </c>
-      <c r="O13" s="10" t="inlineStr">
+      <c r="N13" s="8">
+        <f>SUM(K13:M13)</f>
+        <v/>
+      </c>
+      <c r="O13" s="10">
+        <f>J13+N13</f>
+        <v/>
+      </c>
+      <c r="P13" s="11" t="inlineStr">
         <is>
           <t>17 horas extras noturnas (hora extra + adicional). Feriado 15/08 trabalhado.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>TOTAL ARRAIAL</t>
         </is>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="13">
         <f>SUM(B6:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="13">
         <f>SUM(C6:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="13">
         <f>SUM(D6:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="13">
         <f>SUM(E6:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <f>SUM(F6:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="13">
         <f>SUM(G6:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="13">
         <f>SUM(H6:H13)</f>
         <v/>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="13">
         <f>SUM(I6:I13)</f>
         <v/>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="13">
         <f>SUM(J6:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="13">
         <f>SUM(K6:K13)</f>
         <v/>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="13">
         <f>SUM(L6:L13)</f>
         <v/>
       </c>
-      <c r="M14" s="12">
+      <c r="M14" s="13">
         <f>SUM(M6:M13)</f>
         <v/>
       </c>
-      <c r="N14" s="12">
+      <c r="N14" s="13">
         <f>SUM(N6:N13)</f>
         <v/>
       </c>
-      <c r="O14" s="13" t="n"/>
+      <c r="O14" s="13">
+        <f>SUM(O6:O13)</f>
+        <v/>
+      </c>
+      <c r="P14" s="14" t="n"/>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1178,6 +1232,7 @@
       <c r="M15" s="5" t="n"/>
       <c r="N15" s="5" t="n"/>
       <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1209,22 +1264,26 @@
       <c r="I16" s="7" t="n">
         <v>125</v>
       </c>
-      <c r="J16" s="8" t="n">
-        <v>5773.41</v>
+      <c r="J16" s="8">
+        <f>SUM(B16:I16)</f>
+        <v/>
       </c>
       <c r="K16" s="7" t="n">
         <v>-125</v>
       </c>
-      <c r="L16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="8" t="n">
-        <v>-125</v>
-      </c>
-      <c r="N16" s="9" t="n">
-        <v>5648.41</v>
-      </c>
-      <c r="O16" s="10" t="inlineStr">
+      <c r="L16" s="9" t="n"/>
+      <c r="M16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="8">
+        <f>SUM(K16:M16)</f>
+        <v/>
+      </c>
+      <c r="O16" s="10">
+        <f>J16+N16</f>
+        <v/>
+      </c>
+      <c r="P16" s="11" t="inlineStr">
         <is>
           <t>Não recebe comissão.</t>
         </is>
@@ -1260,22 +1319,26 @@
       <c r="I17" s="7" t="n">
         <v>225</v>
       </c>
-      <c r="J17" s="8" t="n">
-        <v>3648.01</v>
+      <c r="J17" s="8">
+        <f>SUM(B17:I17)</f>
+        <v/>
       </c>
       <c r="K17" s="7" t="n">
         <v>-225</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="L17" s="9" t="n"/>
+      <c r="M17" s="7" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="M17" s="8" t="n">
-        <v>-309.29</v>
-      </c>
-      <c r="N17" s="9" t="n">
-        <v>3338.72</v>
-      </c>
-      <c r="O17" s="10" t="inlineStr"/>
+      <c r="N17" s="8">
+        <f>SUM(K17:M17)</f>
+        <v/>
+      </c>
+      <c r="O17" s="10">
+        <f>J17+N17</f>
+        <v/>
+      </c>
+      <c r="P17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1307,22 +1370,26 @@
       <c r="I18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="8" t="n">
-        <v>0.74</v>
+      <c r="J18" s="8">
+        <f>SUM(B18:I18)</f>
+        <v/>
       </c>
       <c r="K18" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="L18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="O18" s="10" t="inlineStr">
+      <c r="L18" s="9" t="n"/>
+      <c r="M18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="8">
+        <f>SUM(K18:M18)</f>
+        <v/>
+      </c>
+      <c r="O18" s="10">
+        <f>J18+N18</f>
+        <v/>
+      </c>
+      <c r="P18" s="11" t="inlineStr">
         <is>
           <t>Férias de 01 a 30/08 pagas em recibo próprio — conferir o dia 31/08.</t>
         </is>
@@ -1358,22 +1425,26 @@
       <c r="I19" s="7" t="n">
         <v>96</v>
       </c>
-      <c r="J19" s="8" t="n">
-        <v>2728.01</v>
+      <c r="J19" s="8">
+        <f>SUM(B19:I19)</f>
+        <v/>
       </c>
       <c r="K19" s="7" t="n">
         <v>-96</v>
       </c>
-      <c r="L19" s="7" t="n">
+      <c r="L19" s="9" t="n"/>
+      <c r="M19" s="7" t="n">
         <v>-74.29000000000001</v>
       </c>
-      <c r="M19" s="8" t="n">
-        <v>-170.29</v>
-      </c>
-      <c r="N19" s="9" t="n">
-        <v>2557.72</v>
-      </c>
-      <c r="O19" s="10" t="inlineStr"/>
+      <c r="N19" s="8">
+        <f>SUM(K19:M19)</f>
+        <v/>
+      </c>
+      <c r="O19" s="10">
+        <f>J19+N19</f>
+        <v/>
+      </c>
+      <c r="P19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1405,22 +1476,26 @@
       <c r="I20" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="J20" s="8" t="n">
-        <v>1699.36</v>
+      <c r="J20" s="8">
+        <f>SUM(B20:I20)</f>
+        <v/>
       </c>
       <c r="K20" s="7" t="n">
         <v>-10</v>
       </c>
-      <c r="L20" s="7" t="n">
+      <c r="L20" s="9" t="n"/>
+      <c r="M20" s="7" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="M20" s="8" t="n">
-        <v>-94.29000000000001</v>
-      </c>
-      <c r="N20" s="9" t="n">
-        <v>1605.07</v>
-      </c>
-      <c r="O20" s="10" t="inlineStr"/>
+      <c r="N20" s="8">
+        <f>SUM(K20:M20)</f>
+        <v/>
+      </c>
+      <c r="O20" s="10">
+        <f>J20+N20</f>
+        <v/>
+      </c>
+      <c r="P20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1452,86 +1527,94 @@
       <c r="I21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="8" t="n">
-        <v>1621</v>
+      <c r="J21" s="8">
+        <f>SUM(B21:I21)</f>
+        <v/>
       </c>
       <c r="K21" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="L21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="9" t="n">
-        <v>1621</v>
-      </c>
-      <c r="O21" s="10" t="inlineStr">
+      <c r="L21" s="9" t="n"/>
+      <c r="M21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="8">
+        <f>SUM(K21:M21)</f>
+        <v/>
+      </c>
+      <c r="O21" s="10">
+        <f>J21+N21</f>
+        <v/>
+      </c>
+      <c r="P21" s="11" t="inlineStr">
         <is>
           <t>Não recebe comissão (apurado R$ 12,18 fica só como informação).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>TOTAL CENTRO</t>
         </is>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="13">
         <f>SUM(B16:B21)</f>
         <v/>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="13">
         <f>SUM(C16:C21)</f>
         <v/>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="13">
         <f>SUM(D16:D21)</f>
         <v/>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="13">
         <f>SUM(E16:E21)</f>
         <v/>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="13">
         <f>SUM(F16:F21)</f>
         <v/>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="13">
         <f>SUM(G16:G21)</f>
         <v/>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="13">
         <f>SUM(H16:H21)</f>
         <v/>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="13">
         <f>SUM(I16:I21)</f>
         <v/>
       </c>
-      <c r="J22" s="12">
+      <c r="J22" s="13">
         <f>SUM(J16:J21)</f>
         <v/>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="13">
         <f>SUM(K16:K21)</f>
         <v/>
       </c>
-      <c r="L22" s="12">
+      <c r="L22" s="13">
         <f>SUM(L16:L21)</f>
         <v/>
       </c>
-      <c r="M22" s="12">
+      <c r="M22" s="13">
         <f>SUM(M16:M21)</f>
         <v/>
       </c>
-      <c r="N22" s="12">
+      <c r="N22" s="13">
         <f>SUM(N16:N21)</f>
         <v/>
       </c>
-      <c r="O22" s="13" t="n"/>
+      <c r="O22" s="13">
+        <f>SUM(O16:O21)</f>
+        <v/>
+      </c>
+      <c r="P22" s="14" t="n"/>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -1553,6 +1636,7 @@
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n"/>
       <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1584,22 +1668,26 @@
       <c r="I24" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="J24" s="8" t="n">
-        <v>5673.41</v>
+      <c r="J24" s="8">
+        <f>SUM(B24:I24)</f>
+        <v/>
       </c>
       <c r="K24" s="7" t="n">
         <v>-25</v>
       </c>
-      <c r="L24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="8" t="n">
-        <v>-25</v>
-      </c>
-      <c r="N24" s="9" t="n">
-        <v>5648.41</v>
-      </c>
-      <c r="O24" s="10" t="inlineStr">
+      <c r="L24" s="9" t="n"/>
+      <c r="M24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="8">
+        <f>SUM(K24:M24)</f>
+        <v/>
+      </c>
+      <c r="O24" s="10">
+        <f>J24+N24</f>
+        <v/>
+      </c>
+      <c r="P24" s="11" t="inlineStr">
         <is>
           <t>Não recebe comissão.</t>
         </is>
@@ -1635,22 +1723,26 @@
       <c r="I25" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="J25" s="8" t="n">
-        <v>3638.21</v>
+      <c r="J25" s="8">
+        <f>SUM(B25:I25)</f>
+        <v/>
       </c>
       <c r="K25" s="7" t="n">
         <v>-49</v>
       </c>
-      <c r="L25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>-49</v>
-      </c>
-      <c r="N25" s="9" t="n">
-        <v>3589.21</v>
-      </c>
-      <c r="O25" s="10" t="inlineStr">
+      <c r="L25" s="9" t="n"/>
+      <c r="M25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="8">
+        <f>SUM(K25:M25)</f>
+        <v/>
+      </c>
+      <c r="O25" s="10">
+        <f>J25+N25</f>
+        <v/>
+      </c>
+      <c r="P25" s="11" t="inlineStr">
         <is>
           <t>Comissão apurada R$ 825,38 × 2.</t>
         </is>
@@ -1686,22 +1778,26 @@
       <c r="I26" s="7" t="n">
         <v>260</v>
       </c>
-      <c r="J26" s="8" t="n">
-        <v>3994.48</v>
+      <c r="J26" s="8">
+        <f>SUM(B26:I26)</f>
+        <v/>
       </c>
       <c r="K26" s="7" t="n">
         <v>-260</v>
       </c>
-      <c r="L26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="8" t="n">
-        <v>-260</v>
-      </c>
-      <c r="N26" s="9" t="n">
-        <v>3734.48</v>
-      </c>
-      <c r="O26" s="10" t="inlineStr">
+      <c r="L26" s="9" t="n"/>
+      <c r="M26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="8">
+        <f>SUM(K26:M26)</f>
+        <v/>
+      </c>
+      <c r="O26" s="10">
+        <f>J26+N26</f>
+        <v/>
+      </c>
+      <c r="P26" s="11" t="inlineStr">
         <is>
           <t>Comissão apurada R$ 886,30 × 2.</t>
         </is>
@@ -1737,22 +1833,26 @@
       <c r="I27" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="8" t="n">
-        <v>2709.49</v>
+      <c r="J27" s="8">
+        <f>SUM(B27:I27)</f>
+        <v/>
       </c>
       <c r="K27" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="L27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="9" t="n">
-        <v>2709.49</v>
-      </c>
-      <c r="O27" s="10" t="inlineStr">
+      <c r="L27" s="9" t="n"/>
+      <c r="M27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="8">
+        <f>SUM(K27:M27)</f>
+        <v/>
+      </c>
+      <c r="O27" s="10">
+        <f>J27+N27</f>
+        <v/>
+      </c>
+      <c r="P27" s="11" t="inlineStr">
         <is>
           <t>Comissão apurada R$ 235,42 × 2. 40 horas extras.</t>
         </is>
@@ -1788,252 +1888,272 @@
       <c r="I28" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="8" t="n">
-        <v>1920.46</v>
+      <c r="J28" s="8">
+        <f>SUM(B28:I28)</f>
+        <v/>
       </c>
       <c r="K28" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="L28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="9" t="n">
-        <v>1920.46</v>
-      </c>
-      <c r="O28" s="10" t="inlineStr">
+      <c r="L28" s="9" t="n"/>
+      <c r="M28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="8">
+        <f>SUM(K28:M28)</f>
+        <v/>
+      </c>
+      <c r="O28" s="10">
+        <f>J28+N28</f>
+        <v/>
+      </c>
+      <c r="P28" s="11" t="inlineStr">
         <is>
           <t>Comissão apurada R$ 125,58 × 2. Atestado de 02 a 08/09 é competência de setembro.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>TOTAL TRANCOSO</t>
         </is>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="13">
         <f>SUM(B24:B28)</f>
         <v/>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="13">
         <f>SUM(C24:C28)</f>
         <v/>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="13">
         <f>SUM(D24:D28)</f>
         <v/>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="13">
         <f>SUM(E24:E28)</f>
         <v/>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="13">
         <f>SUM(F24:F28)</f>
         <v/>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="13">
         <f>SUM(G24:G28)</f>
         <v/>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="13">
         <f>SUM(H24:H28)</f>
         <v/>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="13">
         <f>SUM(I24:I28)</f>
         <v/>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="13">
         <f>SUM(J24:J28)</f>
         <v/>
       </c>
-      <c r="K29" s="12">
+      <c r="K29" s="13">
         <f>SUM(K24:K28)</f>
         <v/>
       </c>
-      <c r="L29" s="12">
+      <c r="L29" s="13">
         <f>SUM(L24:L28)</f>
         <v/>
       </c>
-      <c r="M29" s="12">
+      <c r="M29" s="13">
         <f>SUM(M24:M28)</f>
         <v/>
       </c>
-      <c r="N29" s="12">
+      <c r="N29" s="13">
         <f>SUM(N24:N28)</f>
         <v/>
       </c>
-      <c r="O29" s="13" t="n"/>
+      <c r="O29" s="13">
+        <f>SUM(O24:O28)</f>
+        <v/>
+      </c>
+      <c r="P29" s="14" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>TOTAL GERAL — 3 LOJAS</t>
         </is>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="16">
         <f>B14+B22+B29</f>
         <v/>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="16">
         <f>C14+C22+C29</f>
         <v/>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="16">
         <f>D14+D22+D29</f>
         <v/>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="16">
         <f>E14+E22+E29</f>
         <v/>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="16">
         <f>F14+F22+F29</f>
         <v/>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="16">
         <f>G14+G22+G29</f>
         <v/>
       </c>
-      <c r="H31" s="15">
+      <c r="H31" s="16">
         <f>H14+H22+H29</f>
         <v/>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="16">
         <f>I14+I22+I29</f>
         <v/>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="16">
         <f>J14+J22+J29</f>
         <v/>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="16">
         <f>K14+K22+K29</f>
         <v/>
       </c>
-      <c r="L31" s="15">
+      <c r="L31" s="16">
         <f>L14+L22+L29</f>
         <v/>
       </c>
-      <c r="M31" s="15">
+      <c r="M31" s="16">
         <f>M14+M22+M29</f>
         <v/>
       </c>
-      <c r="N31" s="15">
+      <c r="N31" s="16">
         <f>N14+N22+N29</f>
         <v/>
       </c>
-      <c r="O31" s="16" t="n"/>
+      <c r="O31" s="16">
+        <f>O14+O22+O29</f>
+        <v/>
+      </c>
+      <c r="P31" s="17" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>O QUE AINDA NÃO ESTÁ NESTE RESUMO — precisa ser somado antes de fechar o holerite:</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>• INSS e IRRF de cada funcionário (cálculo da contabilidade) — por isso a última coluna é LÍQUIDO PARCIAL.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>• Vales adiantados, convênio e descontos de falta do mês.</t>
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>• Convênio e descontos de falta do mês.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>• A coluna ADIANTAMENTO SALARIAL / VALES está em amarelo, para preencher com o valor adiantado a cada um (em negativo). O total de descontos e o líquido se atualizam sozinhos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>• Prêmio cota geral e prêmio pré-vencidos, conforme a apuração de metas de cada loja.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>• Diárias dos folguistas SERGIO (R$ 150,00) e ANA CELIA (R$ 100,00), na loja Centro — vão para o contas a pagar, fora do holerite.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="18" t="inlineStr"/>
-    </row>
     <row r="39">
-      <c r="A39" s="19" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>CRITÉRIOS USADOS:</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>• DSR sobre comissão e horas extras: 5 domingos ÷ 26 dias úteis de agosto/2026 = fator 0,192307.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>• Salário-hora = salário ÷ 220. Hora extra = salário-hora × 1,5 (R$ 11,0523). Adicional noturno = salário-hora × 20% (R$ 1,4736).</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>• Feriado de 15/08 trabalhado sem folga = 1 salário-dia a mais (R$ 54,03).</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>• TRANCOSO paga o dobro da comissão apurada no InovaFarma; os incentivos entram pelo valor simples.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>• Os incentivos são adiantados em dinheiro durante o mês, por isso aparecem como provento e como desconto (ADIANT. INCENT.).</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>• Comissões e incentivos vêm do relatório do InovaFarma de 01/08 a 31/08/2026, extraído em 03/09/2026.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O29"/>
-  <mergeCells count="15">
-    <mergeCell ref="A40:O40"/>
-    <mergeCell ref="A35:O35"/>
-    <mergeCell ref="A43:O43"/>
-    <mergeCell ref="A38:O38"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A42:O42"/>
-    <mergeCell ref="A41:O41"/>
-    <mergeCell ref="A33:O33"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="A44:O44"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="A45:O45"/>
-    <mergeCell ref="A34:O34"/>
-    <mergeCell ref="A39:O39"/>
+  <autoFilter ref="A4:P29"/>
+  <mergeCells count="16">
+    <mergeCell ref="A42:P42"/>
+    <mergeCell ref="A46:P46"/>
+    <mergeCell ref="A36:P36"/>
+    <mergeCell ref="A44:P44"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A37:P37"/>
+    <mergeCell ref="A40:P40"/>
+    <mergeCell ref="A45:P45"/>
+    <mergeCell ref="A39:P39"/>
+    <mergeCell ref="A34:P34"/>
+    <mergeCell ref="A35:P35"/>
+    <mergeCell ref="A38:P38"/>
+    <mergeCell ref="A43:P43"/>
+    <mergeCell ref="A41:P41"/>
+    <mergeCell ref="A33:P33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/relatorios/contabilidade/RESUMO_3_LOJAS_AGOSTO_2026_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RESUMO_3_LOJAS_AGOSTO_2026_pgto_05-09-2026.xlsx
@@ -10,7 +10,7 @@
     <sheet name="RESUMO 3 LOJAS AGO.26" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RESUMO 3 LOJAS AGO.26'!$A$4:$P$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RESUMO 3 LOJAS AGO.26'!$A$4:$Q$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -587,7 +587,8 @@
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="70" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -681,6 +682,11 @@
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>FÉRIAS PAGAS À PARTE (contas a pagar)</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO</t>
         </is>
@@ -707,6 +713,7 @@
       <c r="N5" s="5" t="n"/>
       <c r="O5" s="5" t="n"/>
       <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -757,7 +764,8 @@
         <f>J6+N6</f>
         <v/>
       </c>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="P6" s="9" t="n"/>
+      <c r="Q6" s="11" t="inlineStr">
         <is>
           <t>Não recebe comissão. Dia 15/08 trabalhado com folga compensatória.</t>
         </is>
@@ -812,7 +820,8 @@
         <f>J7+N7</f>
         <v/>
       </c>
-      <c r="P7" s="11" t="inlineStr">
+      <c r="P7" s="9" t="n"/>
+      <c r="Q7" s="11" t="inlineStr">
         <is>
           <t>Comissão fixa de R$ 2.000,00 (apurado R$ 909,51 + complemento R$ 1.090,49). 3 madrugadas = 24 h noturnas.</t>
         </is>
@@ -867,7 +876,8 @@
         <f>J8+N8</f>
         <v/>
       </c>
-      <c r="P8" s="11" t="inlineStr">
+      <c r="P8" s="9" t="n"/>
+      <c r="Q8" s="11" t="inlineStr">
         <is>
           <t>24 horas extras. Adicional noturno fixo de R$ 350,00 — conferir com o ponto.</t>
         </is>
@@ -922,7 +932,8 @@
         <f>J9+N9</f>
         <v/>
       </c>
-      <c r="P9" s="11" t="inlineStr">
+      <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="11" t="inlineStr">
         <is>
           <t>Férias de 01 a 31/08 pagas em recibo próprio (saiu em 04/08, volta em 04/09). Comissão dos dias 01 e 02/08.</t>
         </is>
@@ -977,7 +988,8 @@
         <f>J10+N10</f>
         <v/>
       </c>
-      <c r="P10" s="11" t="inlineStr">
+      <c r="P10" s="9" t="n"/>
+      <c r="Q10" s="11" t="inlineStr">
         <is>
           <t>Feriado 15/08 trabalhado. 2 madrugadas = 16 h noturnas, com folga no dia seguinte.</t>
         </is>
@@ -1032,7 +1044,8 @@
         <f>J11+N11</f>
         <v/>
       </c>
-      <c r="P11" s="11" t="inlineStr">
+      <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="11" t="inlineStr">
         <is>
           <t>Comissão do Arraial (R$ 368,78) + loja Centro (R$ 2,65). Feriado 15/08 trabalhado.</t>
         </is>
@@ -1087,7 +1100,8 @@
         <f>J12+N12</f>
         <v/>
       </c>
-      <c r="P12" s="11" t="inlineStr">
+      <c r="P12" s="9" t="n"/>
+      <c r="Q12" s="11" t="inlineStr">
         <is>
           <t>1º mês completo após a admissão. Feriado 15/08 trabalhado.</t>
         </is>
@@ -1142,7 +1156,8 @@
         <f>J13+N13</f>
         <v/>
       </c>
-      <c r="P13" s="11" t="inlineStr">
+      <c r="P13" s="9" t="n"/>
+      <c r="Q13" s="11" t="inlineStr">
         <is>
           <t>17 horas extras noturnas (hora extra + adicional). Feriado 15/08 trabalhado.</t>
         </is>
@@ -1210,7 +1225,11 @@
         <f>SUM(O6:O13)</f>
         <v/>
       </c>
-      <c r="P14" s="14" t="n"/>
+      <c r="P14" s="13">
+        <f>SUM(P6:P13)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="14" t="n"/>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1233,6 +1252,7 @@
       <c r="N15" s="5" t="n"/>
       <c r="O15" s="5" t="n"/>
       <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1283,7 +1303,8 @@
         <f>J16+N16</f>
         <v/>
       </c>
-      <c r="P16" s="11" t="inlineStr">
+      <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="11" t="inlineStr">
         <is>
           <t>Não recebe comissão.</t>
         </is>
@@ -1338,7 +1359,8 @@
         <f>J17+N17</f>
         <v/>
       </c>
-      <c r="P17" s="11" t="inlineStr"/>
+      <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1389,7 +1411,8 @@
         <f>J18+N18</f>
         <v/>
       </c>
-      <c r="P18" s="11" t="inlineStr">
+      <c r="P18" s="9" t="n"/>
+      <c r="Q18" s="11" t="inlineStr">
         <is>
           <t>Férias de 01 a 30/08 pagas em recibo próprio — conferir o dia 31/08.</t>
         </is>
@@ -1444,7 +1467,8 @@
         <f>J19+N19</f>
         <v/>
       </c>
-      <c r="P19" s="11" t="inlineStr"/>
+      <c r="P19" s="9" t="n"/>
+      <c r="Q19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1495,7 +1519,8 @@
         <f>J20+N20</f>
         <v/>
       </c>
-      <c r="P20" s="11" t="inlineStr"/>
+      <c r="P20" s="9" t="n"/>
+      <c r="Q20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1546,7 +1571,8 @@
         <f>J21+N21</f>
         <v/>
       </c>
-      <c r="P21" s="11" t="inlineStr">
+      <c r="P21" s="9" t="n"/>
+      <c r="Q21" s="11" t="inlineStr">
         <is>
           <t>Não recebe comissão (apurado R$ 12,18 fica só como informação).</t>
         </is>
@@ -1614,7 +1640,11 @@
         <f>SUM(O16:O21)</f>
         <v/>
       </c>
-      <c r="P22" s="14" t="n"/>
+      <c r="P22" s="13">
+        <f>SUM(P16:P21)</f>
+        <v/>
+      </c>
+      <c r="Q22" s="14" t="n"/>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -1637,6 +1667,7 @@
       <c r="N23" s="5" t="n"/>
       <c r="O23" s="5" t="n"/>
       <c r="P23" s="5" t="n"/>
+      <c r="Q23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1687,7 +1718,8 @@
         <f>J24+N24</f>
         <v/>
       </c>
-      <c r="P24" s="11" t="inlineStr">
+      <c r="P24" s="9" t="n"/>
+      <c r="Q24" s="11" t="inlineStr">
         <is>
           <t>Não recebe comissão.</t>
         </is>
@@ -1742,7 +1774,8 @@
         <f>J25+N25</f>
         <v/>
       </c>
-      <c r="P25" s="11" t="inlineStr">
+      <c r="P25" s="9" t="n"/>
+      <c r="Q25" s="11" t="inlineStr">
         <is>
           <t>Comissão apurada R$ 825,38 × 2.</t>
         </is>
@@ -1797,7 +1830,8 @@
         <f>J26+N26</f>
         <v/>
       </c>
-      <c r="P26" s="11" t="inlineStr">
+      <c r="P26" s="9" t="n"/>
+      <c r="Q26" s="11" t="inlineStr">
         <is>
           <t>Comissão apurada R$ 886,30 × 2.</t>
         </is>
@@ -1852,7 +1886,8 @@
         <f>J27+N27</f>
         <v/>
       </c>
-      <c r="P27" s="11" t="inlineStr">
+      <c r="P27" s="9" t="n"/>
+      <c r="Q27" s="11" t="inlineStr">
         <is>
           <t>Comissão apurada R$ 235,42 × 2. 40 horas extras.</t>
         </is>
@@ -1907,7 +1942,8 @@
         <f>J28+N28</f>
         <v/>
       </c>
-      <c r="P28" s="11" t="inlineStr">
+      <c r="P28" s="9" t="n"/>
+      <c r="Q28" s="11" t="inlineStr">
         <is>
           <t>Comissão apurada R$ 125,58 × 2. Atestado de 02 a 08/09 é competência de setembro.</t>
         </is>
@@ -1975,7 +2011,11 @@
         <f>SUM(O24:O28)</f>
         <v/>
       </c>
-      <c r="P29" s="14" t="n"/>
+      <c r="P29" s="13">
+        <f>SUM(P24:P28)</f>
+        <v/>
+      </c>
+      <c r="Q29" s="14" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
@@ -2039,7 +2079,11 @@
         <f>O14+O22+O29</f>
         <v/>
       </c>
-      <c r="P31" s="17" t="n"/>
+      <c r="P31" s="16">
+        <f>P14+P22+P29</f>
+        <v/>
+      </c>
+      <c r="Q31" s="17" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
@@ -2079,81 +2123,89 @@
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
+          <t>• A coluna FÉRIAS PAGAS À PARTE é só lembrete para o contas a pagar: recibo de férias pago fora do holerite, NÃO entra no líquido. Em agosto: JOEL (Arraial, férias de 01 a 31/08) e GENECIR (Centro, férias de 01 a 30/08).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
           <t>• Diárias dos folguistas SERGIO (R$ 150,00) e ANA CELIA (R$ 100,00), na loja Centro — vão para o contas a pagar, fora do holerite.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="19" t="inlineStr"/>
-    </row>
     <row r="40">
-      <c r="A40" s="20" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>CRITÉRIOS USADOS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>• DSR sobre comissão e horas extras: 5 domingos ÷ 26 dias úteis de agosto/2026 = fator 0,192307.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>• Salário-hora = salário ÷ 220. Hora extra = salário-hora × 1,5 (R$ 11,0523). Adicional noturno = salário-hora × 20% (R$ 1,4736).</t>
+          <t>• DSR sobre comissão e horas extras: 5 domingos ÷ 26 dias úteis de agosto/2026 = fator 0,192307.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>• Feriado de 15/08 trabalhado sem folga = 1 salário-dia a mais (R$ 54,03).</t>
+          <t>• Salário-hora = salário ÷ 220. Hora extra = salário-hora × 1,5 (R$ 11,0523). Adicional noturno = salário-hora × 20% (R$ 1,4736).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>• TRANCOSO paga o dobro da comissão apurada no InovaFarma; os incentivos entram pelo valor simples.</t>
+          <t>• Feriado de 15/08 trabalhado sem folga = 1 salário-dia a mais (R$ 54,03).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>• Os incentivos são adiantados em dinheiro durante o mês, por isso aparecem como provento e como desconto (ADIANT. INCENT.).</t>
+          <t>• TRANCOSO paga o dobro da comissão apurada no InovaFarma; os incentivos entram pelo valor simples.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
         <is>
+          <t>• Os incentivos são adiantados em dinheiro durante o mês, por isso aparecem como provento e como desconto (ADIANT. INCENT.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
           <t>• Comissões e incentivos vêm do relatório do InovaFarma de 01/08 a 31/08/2026, extraído em 03/09/2026.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P29"/>
-  <mergeCells count="16">
-    <mergeCell ref="A42:P42"/>
-    <mergeCell ref="A46:P46"/>
-    <mergeCell ref="A36:P36"/>
-    <mergeCell ref="A44:P44"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="A37:P37"/>
-    <mergeCell ref="A40:P40"/>
-    <mergeCell ref="A45:P45"/>
-    <mergeCell ref="A39:P39"/>
-    <mergeCell ref="A34:P34"/>
-    <mergeCell ref="A35:P35"/>
-    <mergeCell ref="A38:P38"/>
-    <mergeCell ref="A43:P43"/>
-    <mergeCell ref="A41:P41"/>
-    <mergeCell ref="A33:P33"/>
+  <autoFilter ref="A4:Q29"/>
+  <mergeCells count="17">
+    <mergeCell ref="A44:Q44"/>
+    <mergeCell ref="A40:Q40"/>
+    <mergeCell ref="A46:Q46"/>
+    <mergeCell ref="A39:Q39"/>
+    <mergeCell ref="A34:Q34"/>
+    <mergeCell ref="A35:Q35"/>
+    <mergeCell ref="A43:Q43"/>
+    <mergeCell ref="A38:Q38"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="A41:Q41"/>
+    <mergeCell ref="A33:Q33"/>
+    <mergeCell ref="A45:Q45"/>
+    <mergeCell ref="A47:Q47"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A37:Q37"/>
+    <mergeCell ref="A36:Q36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/relatorios/contabilidade/RESUMO_3_LOJAS_AGOSTO_2026_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RESUMO_3_LOJAS_AGOSTO_2026_pgto_05-09-2026.xlsx
@@ -10,7 +10,7 @@
     <sheet name="RESUMO 3 LOJAS AGO.26" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RESUMO 3 LOJAS AGO.26'!$A$4:$Q$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RESUMO 3 LOJAS AGO.26'!$A$4:$Y$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00;-R$ #,##0.00;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,7 +84,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -92,14 +92,8 @@
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -128,17 +122,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF0F0"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -168,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -184,24 +173,21 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -569,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:Y49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -581,14 +567,22 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="70" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -653,40 +647,80 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>PRÊMIOS / BONIFIC.</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>DSR S/ HORA EXTRA</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>SAL. FAMÍLIA</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>INSUF. SALDO</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>TOTAL PROVENTOS</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>ADIANT. INCENT.</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>VALE TRANSP. 6%</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>VALE TRANSP.</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>INSS</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>IRRF</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>TOTAL DESCONTOS</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>LÍQUIDO PARCIAL</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>LÍQUIDO</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>LÍQUIDO HOLERITE BETEL</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>DIFERENÇA</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>FÉRIAS PAGAS À PARTE (contas a pagar)</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO</t>
         </is>
@@ -714,6 +748,14 @@
       <c r="O5" s="5" t="n"/>
       <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -745,27 +787,54 @@
       <c r="I6" s="7" t="n">
         <v>199</v>
       </c>
-      <c r="J6" s="8">
-        <f>SUM(B6:I6)</f>
-        <v/>
+      <c r="J6" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="8">
+        <f>SUM(B6:M6)</f>
+        <v/>
+      </c>
+      <c r="O6" s="7" t="n">
         <v>-199</v>
       </c>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="8">
-        <f>SUM(K6:M6)</f>
-        <v/>
-      </c>
-      <c r="O6" s="10">
-        <f>J6+N6</f>
-        <v/>
-      </c>
-      <c r="P6" s="9" t="n"/>
-      <c r="Q6" s="11" t="inlineStr">
+      <c r="P6" s="7" t="n">
+        <v>-705</v>
+      </c>
+      <c r="Q6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7" t="n">
+        <v>-592.27</v>
+      </c>
+      <c r="S6" s="7" t="n">
+        <v>-251.04</v>
+      </c>
+      <c r="T6" s="8">
+        <f>SUM(O6:S6)</f>
+        <v/>
+      </c>
+      <c r="U6" s="9">
+        <f>N6+T6</f>
+        <v/>
+      </c>
+      <c r="V6" s="7" t="n">
+        <v>4100.1</v>
+      </c>
+      <c r="W6" s="10">
+        <f>ROUND(U6-V6,2)</f>
+        <v/>
+      </c>
+      <c r="X6" s="11" t="n"/>
+      <c r="Y6" s="12" t="inlineStr">
         <is>
           <t>Não recebe comissão. Dia 15/08 trabalhado com folga compensatória.</t>
         </is>
@@ -801,29 +870,56 @@
       <c r="I7" s="7" t="n">
         <v>189</v>
       </c>
-      <c r="J7" s="8">
-        <f>SUM(B7:I7)</f>
-        <v/>
+      <c r="J7" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="8">
+        <f>SUM(B7:M7)</f>
+        <v/>
+      </c>
+      <c r="O7" s="7" t="n">
         <v>-189</v>
       </c>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="8">
-        <f>SUM(K7:M7)</f>
-        <v/>
-      </c>
-      <c r="O7" s="10">
-        <f>J7+N7</f>
-        <v/>
-      </c>
-      <c r="P7" s="9" t="n"/>
-      <c r="Q7" s="11" t="inlineStr">
-        <is>
-          <t>Comissão fixa de R$ 2.000,00 (apurado R$ 909,51 + complemento R$ 1.090,49). 3 madrugadas = 24 h noturnas.</t>
+      <c r="P7" s="7" t="n">
+        <v>-2694</v>
+      </c>
+      <c r="Q7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7" t="n">
+        <v>-480.71</v>
+      </c>
+      <c r="S7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="8">
+        <f>SUM(O7:S7)</f>
+        <v/>
+      </c>
+      <c r="U7" s="9">
+        <f>N7+T7</f>
+        <v/>
+      </c>
+      <c r="V7" s="7" t="n">
+        <v>1676.78</v>
+      </c>
+      <c r="W7" s="10">
+        <f>ROUND(U7-V7,2)</f>
+        <v/>
+      </c>
+      <c r="X7" s="11" t="n"/>
+      <c r="Y7" s="12" t="inlineStr">
+        <is>
+          <t>Comissão fixa de R$ 2.000,00 (apurado R$ 909,51 + complemento). 3 madrugadas = 24 h noturnas.</t>
         </is>
       </c>
     </row>
@@ -837,7 +933,7 @@
         <v>1621</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>265.26</v>
+        <v>265.25</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>350</v>
@@ -857,29 +953,56 @@
       <c r="I8" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="J8" s="8">
-        <f>SUM(B8:I8)</f>
-        <v/>
+      <c r="J8" s="7" t="n">
+        <v>350</v>
       </c>
       <c r="K8" s="7" t="n">
+        <v>51.01</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="8">
+        <f>SUM(B8:M8)</f>
+        <v/>
+      </c>
+      <c r="O8" s="7" t="n">
         <v>-73</v>
       </c>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="7" t="n">
+      <c r="P8" s="7" t="n">
+        <v>-247</v>
+      </c>
+      <c r="Q8" s="7" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="N8" s="8">
-        <f>SUM(K8:M8)</f>
-        <v/>
-      </c>
-      <c r="O8" s="10">
-        <f>J8+N8</f>
-        <v/>
-      </c>
-      <c r="P8" s="9" t="n"/>
-      <c r="Q8" s="11" t="inlineStr">
-        <is>
-          <t>24 horas extras. Adicional noturno fixo de R$ 350,00 — conferir com o ponto.</t>
+      <c r="R8" s="7" t="n">
+        <v>-336.19</v>
+      </c>
+      <c r="S8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="8">
+        <f>SUM(O8:S8)</f>
+        <v/>
+      </c>
+      <c r="U8" s="9">
+        <f>N8+T8</f>
+        <v/>
+      </c>
+      <c r="V8" s="7" t="n">
+        <v>3062.58</v>
+      </c>
+      <c r="W8" s="10">
+        <f>ROUND(U8-V8,2)</f>
+        <v/>
+      </c>
+      <c r="X8" s="11" t="n"/>
+      <c r="Y8" s="12" t="inlineStr">
+        <is>
+          <t>24 horas extras. Adicional noturno de R$ 350,00.</t>
         </is>
       </c>
     </row>
@@ -913,29 +1036,56 @@
       <c r="I9" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="J9" s="8">
-        <f>SUM(B9:I9)</f>
-        <v/>
+      <c r="J9" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>67.54000000000001</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N9" s="8">
+        <f>SUM(B9:M9)</f>
+        <v/>
+      </c>
+      <c r="O9" s="7" t="n">
         <v>-22</v>
       </c>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="8">
-        <f>SUM(K9:M9)</f>
-        <v/>
-      </c>
-      <c r="O9" s="10">
-        <f>J9+N9</f>
-        <v/>
-      </c>
-      <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="11" t="inlineStr">
-        <is>
-          <t>Férias de 01 a 31/08 pagas em recibo próprio (saiu em 04/08, volta em 04/09). Comissão dos dias 01 e 02/08.</t>
+      <c r="P9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="R9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="8">
+        <f>SUM(O9:S9)</f>
+        <v/>
+      </c>
+      <c r="U9" s="9">
+        <f>N9+T9</f>
+        <v/>
+      </c>
+      <c r="V9" s="7" t="n">
+        <v>67.54000000000001</v>
+      </c>
+      <c r="W9" s="10">
+        <f>ROUND(U9-V9,2)</f>
+        <v/>
+      </c>
+      <c r="X9" s="11" t="n"/>
+      <c r="Y9" s="12" t="inlineStr">
+        <is>
+          <t>Férias de 01 a 31/08 em recibo próprio. A comissão de R$ 103,31 e o DSR NÃO entraram no holerite — verificar.</t>
         </is>
       </c>
     </row>
@@ -949,7 +1099,7 @@
         <v>1621</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>54.03</v>
+        <v>53.97</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>23.58</v>
@@ -958,7 +1108,7 @@
         <v>1141.03</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>229.82</v>
+        <v>229.81</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>0</v>
@@ -969,27 +1119,54 @@
       <c r="I10" s="7" t="n">
         <v>192</v>
       </c>
-      <c r="J10" s="8">
-        <f>SUM(B10:I10)</f>
-        <v/>
+      <c r="J10" s="7" t="n">
+        <v>350</v>
       </c>
       <c r="K10" s="7" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="8">
+        <f>SUM(B10:M10)</f>
+        <v/>
+      </c>
+      <c r="O10" s="7" t="n">
         <v>-192</v>
       </c>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="7" t="n">
+      <c r="P10" s="7" t="n">
+        <v>-2351</v>
+      </c>
+      <c r="Q10" s="7" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="N10" s="8">
-        <f>SUM(K10:M10)</f>
-        <v/>
-      </c>
-      <c r="O10" s="10">
-        <f>J10+N10</f>
-        <v/>
-      </c>
-      <c r="P10" s="9" t="n"/>
-      <c r="Q10" s="11" t="inlineStr">
+      <c r="R10" s="7" t="n">
+        <v>-337.12</v>
+      </c>
+      <c r="S10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="8">
+        <f>SUM(O10:S10)</f>
+        <v/>
+      </c>
+      <c r="U10" s="9">
+        <f>N10+T10</f>
+        <v/>
+      </c>
+      <c r="V10" s="7" t="n">
+        <v>965.35</v>
+      </c>
+      <c r="W10" s="10">
+        <f>ROUND(U10-V10,2)</f>
+        <v/>
+      </c>
+      <c r="X10" s="11" t="n"/>
+      <c r="Y10" s="12" t="inlineStr">
         <is>
           <t>Feriado 15/08 trabalhado. 2 madrugadas = 16 h noturnas, com folga no dia seguinte.</t>
         </is>
@@ -1005,7 +1182,7 @@
         <v>1621</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>54.03</v>
+        <v>53.97</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>0</v>
@@ -1014,7 +1191,7 @@
         <v>371.43</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>81.81999999999999</v>
+        <v>81.81</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>810.5</v>
@@ -1025,27 +1202,54 @@
       <c r="I11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="J11" s="8">
-        <f>SUM(B11:I11)</f>
-        <v/>
+      <c r="J11" s="7" t="n">
+        <v>350</v>
       </c>
       <c r="K11" s="7" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8">
+        <f>SUM(B11:M11)</f>
+        <v/>
+      </c>
+      <c r="O11" s="7" t="n">
         <v>-10</v>
       </c>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="8">
-        <f>SUM(K11:M11)</f>
-        <v/>
-      </c>
-      <c r="O11" s="10">
-        <f>J11+N11</f>
-        <v/>
-      </c>
-      <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="11" t="inlineStr">
+      <c r="P11" s="7" t="n">
+        <v>-310</v>
+      </c>
+      <c r="Q11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7" t="n">
+        <v>-284.48</v>
+      </c>
+      <c r="S11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="8">
+        <f>SUM(O11:S11)</f>
+        <v/>
+      </c>
+      <c r="U11" s="9">
+        <f>N11+T11</f>
+        <v/>
+      </c>
+      <c r="V11" s="7" t="n">
+        <v>2704.61</v>
+      </c>
+      <c r="W11" s="10">
+        <f>ROUND(U11-V11,2)</f>
+        <v/>
+      </c>
+      <c r="X11" s="11" t="n"/>
+      <c r="Y11" s="12" t="inlineStr">
         <is>
           <t>Comissão do Arraial (R$ 368,78) + loja Centro (R$ 2,65). Feriado 15/08 trabalhado.</t>
         </is>
@@ -1061,7 +1265,7 @@
         <v>1621</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>54.03</v>
+        <v>53.97</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>0</v>
@@ -1070,7 +1274,7 @@
         <v>241.5</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>56.83</v>
+        <v>56.82</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>0</v>
@@ -1081,27 +1285,54 @@
       <c r="I12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="8">
-        <f>SUM(B12:I12)</f>
-        <v/>
+      <c r="J12" s="7" t="n">
+        <v>250</v>
       </c>
       <c r="K12" s="7" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="8">
+        <f>SUM(B12:M12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="8">
-        <f>SUM(K12:M12)</f>
-        <v/>
-      </c>
-      <c r="O12" s="10">
-        <f>J12+N12</f>
-        <v/>
-      </c>
-      <c r="P12" s="9" t="n"/>
-      <c r="Q12" s="11" t="inlineStr">
+      <c r="P12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7" t="n">
+        <v>-176.71</v>
+      </c>
+      <c r="S12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="8">
+        <f>SUM(O12:S12)</f>
+        <v/>
+      </c>
+      <c r="U12" s="9">
+        <f>N12+T12</f>
+        <v/>
+      </c>
+      <c r="V12" s="7" t="n">
+        <v>2056.96</v>
+      </c>
+      <c r="W12" s="10">
+        <f>ROUND(U12-V12,2)</f>
+        <v/>
+      </c>
+      <c r="X12" s="11" t="n"/>
+      <c r="Y12" s="12" t="inlineStr">
         <is>
           <t>1º mês completo após a admissão. Feriado 15/08 trabalhado.</t>
         </is>
@@ -1117,7 +1348,7 @@
         <v>1621</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>241.92</v>
+        <v>241.86</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>25.05</v>
@@ -1126,7 +1357,7 @@
         <v>243.14</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>93.28</v>
+        <v>93.27</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>0</v>
@@ -1137,99 +1368,158 @@
       <c r="I13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="8">
-        <f>SUM(B13:I13)</f>
-        <v/>
+      <c r="J13" s="7" t="n">
+        <v>250</v>
       </c>
       <c r="K13" s="7" t="n">
+        <v>46.51</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8">
+        <f>SUM(B13:M13)</f>
+        <v/>
+      </c>
+      <c r="O13" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="L13" s="9" t="n"/>
-      <c r="M13" s="7" t="n">
+      <c r="P13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="7" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="N13" s="8">
-        <f>SUM(K13:M13)</f>
-        <v/>
-      </c>
-      <c r="O13" s="10">
-        <f>J13+N13</f>
-        <v/>
-      </c>
-      <c r="P13" s="9" t="n"/>
-      <c r="Q13" s="11" t="inlineStr">
-        <is>
-          <t>17 horas extras noturnas (hora extra + adicional). Feriado 15/08 trabalhado.</t>
+      <c r="R13" s="7" t="n">
+        <v>-230.27</v>
+      </c>
+      <c r="S13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="8">
+        <f>SUM(O13:S13)</f>
+        <v/>
+      </c>
+      <c r="U13" s="9">
+        <f>N13+T13</f>
+        <v/>
+      </c>
+      <c r="V13" s="7" t="n">
+        <v>2514.26</v>
+      </c>
+      <c r="W13" s="10">
+        <f>ROUND(U13-V13,2)</f>
+        <v/>
+      </c>
+      <c r="X13" s="11" t="n"/>
+      <c r="Y13" s="12" t="inlineStr">
+        <is>
+          <t>17 horas extras noturnas e o feriado de 15/08.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>TOTAL ARRAIAL</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="10">
         <f>SUM(B6:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="10">
         <f>SUM(C6:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="10">
         <f>SUM(D6:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="10">
         <f>SUM(E6:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="10">
         <f>SUM(F6:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="10">
         <f>SUM(G6:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="10">
         <f>SUM(H6:H13)</f>
         <v/>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="10">
         <f>SUM(I6:I13)</f>
         <v/>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="10">
         <f>SUM(J6:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="10">
         <f>SUM(K6:K13)</f>
         <v/>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="10">
         <f>SUM(L6:L13)</f>
         <v/>
       </c>
-      <c r="M14" s="13">
+      <c r="M14" s="10">
         <f>SUM(M6:M13)</f>
         <v/>
       </c>
-      <c r="N14" s="13">
+      <c r="N14" s="10">
         <f>SUM(N6:N13)</f>
         <v/>
       </c>
-      <c r="O14" s="13">
+      <c r="O14" s="10">
         <f>SUM(O6:O13)</f>
         <v/>
       </c>
-      <c r="P14" s="13">
+      <c r="P14" s="10">
         <f>SUM(P6:P13)</f>
         <v/>
       </c>
-      <c r="Q14" s="14" t="n"/>
+      <c r="Q14" s="10">
+        <f>SUM(Q6:Q13)</f>
+        <v/>
+      </c>
+      <c r="R14" s="10">
+        <f>SUM(R6:R13)</f>
+        <v/>
+      </c>
+      <c r="S14" s="10">
+        <f>SUM(S6:S13)</f>
+        <v/>
+      </c>
+      <c r="T14" s="10">
+        <f>SUM(T6:T13)</f>
+        <v/>
+      </c>
+      <c r="U14" s="10">
+        <f>SUM(U6:U13)</f>
+        <v/>
+      </c>
+      <c r="V14" s="10">
+        <f>SUM(V6:V13)</f>
+        <v/>
+      </c>
+      <c r="W14" s="10">
+        <f>SUM(W6:W13)</f>
+        <v/>
+      </c>
+      <c r="X14" s="10">
+        <f>SUM(X6:X13)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="14" t="n"/>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1253,6 +1543,14 @@
       <c r="O15" s="5" t="n"/>
       <c r="P15" s="5" t="n"/>
       <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="5" t="n"/>
+      <c r="U15" s="5" t="n"/>
+      <c r="V15" s="5" t="n"/>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+      <c r="Y15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1284,27 +1582,54 @@
       <c r="I16" s="7" t="n">
         <v>125</v>
       </c>
-      <c r="J16" s="8">
-        <f>SUM(B16:I16)</f>
-        <v/>
+      <c r="J16" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="8">
+        <f>SUM(B16:M16)</f>
+        <v/>
+      </c>
+      <c r="O16" s="7" t="n">
         <v>-125</v>
       </c>
-      <c r="L16" s="9" t="n"/>
-      <c r="M16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="8">
-        <f>SUM(K16:M16)</f>
-        <v/>
-      </c>
-      <c r="O16" s="10">
-        <f>J16+N16</f>
-        <v/>
-      </c>
-      <c r="P16" s="9" t="n"/>
-      <c r="Q16" s="11" t="inlineStr">
+      <c r="P16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="7" t="n">
+        <v>-592.27</v>
+      </c>
+      <c r="S16" s="7" t="n">
+        <v>-251.04</v>
+      </c>
+      <c r="T16" s="8">
+        <f>SUM(O16:S16)</f>
+        <v/>
+      </c>
+      <c r="U16" s="9">
+        <f>N16+T16</f>
+        <v/>
+      </c>
+      <c r="V16" s="7" t="n">
+        <v>4805.1</v>
+      </c>
+      <c r="W16" s="10">
+        <f>ROUND(U16-V16,2)</f>
+        <v/>
+      </c>
+      <c r="X16" s="11" t="n"/>
+      <c r="Y16" s="12" t="inlineStr">
         <is>
           <t>Não recebe comissão.</t>
         </is>
@@ -1340,27 +1665,54 @@
       <c r="I17" s="7" t="n">
         <v>225</v>
       </c>
-      <c r="J17" s="8">
-        <f>SUM(B17:I17)</f>
-        <v/>
+      <c r="J17" s="7" t="n">
+        <v>600</v>
       </c>
       <c r="K17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8">
+        <f>SUM(B17:M17)</f>
+        <v/>
+      </c>
+      <c r="O17" s="7" t="n">
         <v>-225</v>
       </c>
-      <c r="L17" s="9" t="n"/>
-      <c r="M17" s="7" t="n">
+      <c r="P17" s="7" t="n">
+        <v>-2192</v>
+      </c>
+      <c r="Q17" s="7" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="N17" s="8">
-        <f>SUM(K17:M17)</f>
-        <v/>
-      </c>
-      <c r="O17" s="10">
-        <f>J17+N17</f>
-        <v/>
-      </c>
-      <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="11" t="inlineStr"/>
+      <c r="R17" s="7" t="n">
+        <v>-371.35</v>
+      </c>
+      <c r="S17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="8">
+        <f>SUM(O17:S17)</f>
+        <v/>
+      </c>
+      <c r="U17" s="9">
+        <f>N17+T17</f>
+        <v/>
+      </c>
+      <c r="V17" s="7" t="n">
+        <v>1375.37</v>
+      </c>
+      <c r="W17" s="10">
+        <f>ROUND(U17-V17,2)</f>
+        <v/>
+      </c>
+      <c r="X17" s="11" t="n"/>
+      <c r="Y17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1392,29 +1744,56 @@
       <c r="I18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="8">
-        <f>SUM(B18:I18)</f>
-        <v/>
+      <c r="J18" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N18" s="8">
+        <f>SUM(B18:M18)</f>
+        <v/>
+      </c>
+      <c r="O18" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="L18" s="9" t="n"/>
-      <c r="M18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="8">
-        <f>SUM(K18:M18)</f>
-        <v/>
-      </c>
-      <c r="O18" s="10">
-        <f>J18+N18</f>
-        <v/>
-      </c>
-      <c r="P18" s="9" t="n"/>
-      <c r="Q18" s="11" t="inlineStr">
-        <is>
-          <t>Férias de 01 a 30/08 pagas em recibo próprio — conferir o dia 31/08.</t>
+      <c r="P18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="7" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="R18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="8">
+        <f>SUM(O18:S18)</f>
+        <v/>
+      </c>
+      <c r="U18" s="9">
+        <f>N18+T18</f>
+        <v/>
+      </c>
+      <c r="V18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="10">
+        <f>ROUND(U18-V18,2)</f>
+        <v/>
+      </c>
+      <c r="X18" s="11" t="n"/>
+      <c r="Y18" s="12" t="inlineStr">
+        <is>
+          <t>Férias de 01 a 30/08 em recibo próprio. A comissão residual de R$ 0,62 não entrou no holerite.</t>
         </is>
       </c>
     </row>
@@ -1448,27 +1827,58 @@
       <c r="I19" s="7" t="n">
         <v>96</v>
       </c>
-      <c r="J19" s="8">
-        <f>SUM(B19:I19)</f>
-        <v/>
+      <c r="J19" s="7" t="n">
+        <v>250</v>
       </c>
       <c r="K19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8">
+        <f>SUM(B19:M19)</f>
+        <v/>
+      </c>
+      <c r="O19" s="7" t="n">
         <v>-96</v>
       </c>
-      <c r="L19" s="9" t="n"/>
-      <c r="M19" s="7" t="n">
-        <v>-74.29000000000001</v>
-      </c>
-      <c r="N19" s="8">
-        <f>SUM(K19:M19)</f>
-        <v/>
-      </c>
-      <c r="O19" s="10">
-        <f>J19+N19</f>
-        <v/>
-      </c>
-      <c r="P19" s="9" t="n"/>
-      <c r="Q19" s="11" t="inlineStr"/>
+      <c r="P19" s="7" t="n">
+        <v>-1955</v>
+      </c>
+      <c r="Q19" s="7" t="n">
+        <v>-68.08</v>
+      </c>
+      <c r="R19" s="7" t="n">
+        <v>-235.06</v>
+      </c>
+      <c r="S19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="8">
+        <f>SUM(O19:S19)</f>
+        <v/>
+      </c>
+      <c r="U19" s="9">
+        <f>N19+T19</f>
+        <v/>
+      </c>
+      <c r="V19" s="7" t="n">
+        <v>623.87</v>
+      </c>
+      <c r="W19" s="10">
+        <f>ROUND(U19-V19,2)</f>
+        <v/>
+      </c>
+      <c r="X19" s="11" t="n"/>
+      <c r="Y19" s="12" t="inlineStr">
+        <is>
+          <t>Férias de 01 a 30/09/2026 — entram na folha de setembro.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1500,27 +1910,54 @@
       <c r="I20" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="J20" s="8">
-        <f>SUM(B20:I20)</f>
-        <v/>
+      <c r="J20" s="7" t="n">
+        <v>100</v>
       </c>
       <c r="K20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="8">
+        <f>SUM(B20:M20)</f>
+        <v/>
+      </c>
+      <c r="O20" s="7" t="n">
         <v>-10</v>
       </c>
-      <c r="L20" s="9" t="n"/>
-      <c r="M20" s="7" t="n">
+      <c r="P20" s="7" t="n">
+        <v>-200</v>
+      </c>
+      <c r="Q20" s="7" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="N20" s="8">
-        <f>SUM(K20:M20)</f>
-        <v/>
-      </c>
-      <c r="O20" s="10">
-        <f>J20+N20</f>
-        <v/>
-      </c>
-      <c r="P20" s="9" t="n"/>
-      <c r="Q20" s="11" t="inlineStr"/>
+      <c r="R20" s="7" t="n">
+        <v>-136.72</v>
+      </c>
+      <c r="S20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="8">
+        <f>SUM(O20:S20)</f>
+        <v/>
+      </c>
+      <c r="U20" s="9">
+        <f>N20+T20</f>
+        <v/>
+      </c>
+      <c r="V20" s="7" t="n">
+        <v>1368.35</v>
+      </c>
+      <c r="W20" s="10">
+        <f>ROUND(U20-V20,2)</f>
+        <v/>
+      </c>
+      <c r="X20" s="11" t="n"/>
+      <c r="Y20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1552,99 +1989,156 @@
       <c r="I21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="8">
-        <f>SUM(B21:I21)</f>
-        <v/>
+      <c r="J21" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="8">
+        <f>SUM(B21:M21)</f>
+        <v/>
+      </c>
+      <c r="O21" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="L21" s="9" t="n"/>
-      <c r="M21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="8">
-        <f>SUM(K21:M21)</f>
-        <v/>
-      </c>
-      <c r="O21" s="10">
-        <f>J21+N21</f>
-        <v/>
-      </c>
-      <c r="P21" s="9" t="n"/>
-      <c r="Q21" s="11" t="inlineStr">
-        <is>
-          <t>Não recebe comissão (apurado R$ 12,18 fica só como informação).</t>
+      <c r="P21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="8">
+        <f>SUM(O21:S21)</f>
+        <v/>
+      </c>
+      <c r="U21" s="9">
+        <f>N21+T21</f>
+        <v/>
+      </c>
+      <c r="V21" s="7" t="n"/>
+      <c r="W21" s="10">
+        <f>ROUND(U21-V21,2)</f>
+        <v/>
+      </c>
+      <c r="X21" s="11" t="n"/>
+      <c r="Y21" s="12" t="inlineStr">
+        <is>
+          <t>NÃO CONSTA no holerite de agosto emitido pela Betel para esta loja — verificar em qual empresa foi lançado.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>TOTAL CENTRO</t>
         </is>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="10">
         <f>SUM(B16:B21)</f>
         <v/>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="10">
         <f>SUM(C16:C21)</f>
         <v/>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="10">
         <f>SUM(D16:D21)</f>
         <v/>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="10">
         <f>SUM(E16:E21)</f>
         <v/>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="10">
         <f>SUM(F16:F21)</f>
         <v/>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="10">
         <f>SUM(G16:G21)</f>
         <v/>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="10">
         <f>SUM(H16:H21)</f>
         <v/>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="10">
         <f>SUM(I16:I21)</f>
         <v/>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="10">
         <f>SUM(J16:J21)</f>
         <v/>
       </c>
-      <c r="K22" s="13">
+      <c r="K22" s="10">
         <f>SUM(K16:K21)</f>
         <v/>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="10">
         <f>SUM(L16:L21)</f>
         <v/>
       </c>
-      <c r="M22" s="13">
+      <c r="M22" s="10">
         <f>SUM(M16:M21)</f>
         <v/>
       </c>
-      <c r="N22" s="13">
+      <c r="N22" s="10">
         <f>SUM(N16:N21)</f>
         <v/>
       </c>
-      <c r="O22" s="13">
+      <c r="O22" s="10">
         <f>SUM(O16:O21)</f>
         <v/>
       </c>
-      <c r="P22" s="13">
+      <c r="P22" s="10">
         <f>SUM(P16:P21)</f>
         <v/>
       </c>
-      <c r="Q22" s="14" t="n"/>
+      <c r="Q22" s="10">
+        <f>SUM(Q16:Q21)</f>
+        <v/>
+      </c>
+      <c r="R22" s="10">
+        <f>SUM(R16:R21)</f>
+        <v/>
+      </c>
+      <c r="S22" s="10">
+        <f>SUM(S16:S21)</f>
+        <v/>
+      </c>
+      <c r="T22" s="10">
+        <f>SUM(T16:T21)</f>
+        <v/>
+      </c>
+      <c r="U22" s="10">
+        <f>SUM(U16:U21)</f>
+        <v/>
+      </c>
+      <c r="V22" s="10">
+        <f>SUM(V16:V21)</f>
+        <v/>
+      </c>
+      <c r="W22" s="10">
+        <f>SUM(W16:W21)</f>
+        <v/>
+      </c>
+      <c r="X22" s="10">
+        <f>SUM(X16:X21)</f>
+        <v/>
+      </c>
+      <c r="Y22" s="14" t="n"/>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -1668,6 +2162,14 @@
       <c r="O23" s="5" t="n"/>
       <c r="P23" s="5" t="n"/>
       <c r="Q23" s="5" t="n"/>
+      <c r="R23" s="5" t="n"/>
+      <c r="S23" s="5" t="n"/>
+      <c r="T23" s="5" t="n"/>
+      <c r="U23" s="5" t="n"/>
+      <c r="V23" s="5" t="n"/>
+      <c r="W23" s="5" t="n"/>
+      <c r="X23" s="5" t="n"/>
+      <c r="Y23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1699,27 +2201,54 @@
       <c r="I24" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="J24" s="8">
-        <f>SUM(B24:I24)</f>
-        <v/>
+      <c r="J24" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="8">
+        <f>SUM(B24:M24)</f>
+        <v/>
+      </c>
+      <c r="O24" s="7" t="n">
         <v>-25</v>
       </c>
-      <c r="L24" s="9" t="n"/>
-      <c r="M24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="8">
-        <f>SUM(K24:M24)</f>
-        <v/>
-      </c>
-      <c r="O24" s="10">
-        <f>J24+N24</f>
-        <v/>
-      </c>
-      <c r="P24" s="9" t="n"/>
-      <c r="Q24" s="11" t="inlineStr">
+      <c r="P24" s="7" t="n">
+        <v>-810</v>
+      </c>
+      <c r="Q24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="7" t="n">
+        <v>-592.27</v>
+      </c>
+      <c r="S24" s="7" t="n">
+        <v>-251.04</v>
+      </c>
+      <c r="T24" s="8">
+        <f>SUM(O24:S24)</f>
+        <v/>
+      </c>
+      <c r="U24" s="9">
+        <f>N24+T24</f>
+        <v/>
+      </c>
+      <c r="V24" s="7" t="n">
+        <v>3995.1</v>
+      </c>
+      <c r="W24" s="10">
+        <f>ROUND(U24-V24,2)</f>
+        <v/>
+      </c>
+      <c r="X24" s="11" t="n"/>
+      <c r="Y24" s="12" t="inlineStr">
         <is>
           <t>Não recebe comissão.</t>
         </is>
@@ -1755,27 +2284,54 @@
       <c r="I25" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="J25" s="8">
-        <f>SUM(B25:I25)</f>
-        <v/>
+      <c r="J25" s="7" t="n">
+        <v>200</v>
       </c>
       <c r="K25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="8">
+        <f>SUM(B25:M25)</f>
+        <v/>
+      </c>
+      <c r="O25" s="7" t="n">
         <v>-49</v>
       </c>
-      <c r="L25" s="9" t="n"/>
-      <c r="M25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="8">
-        <f>SUM(K25:M25)</f>
-        <v/>
-      </c>
-      <c r="O25" s="10">
-        <f>J25+N25</f>
-        <v/>
-      </c>
-      <c r="P25" s="9" t="n"/>
-      <c r="Q25" s="11" t="inlineStr">
+      <c r="P25" s="7" t="n">
+        <v>-465</v>
+      </c>
+      <c r="Q25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="7" t="n">
+        <v>-343.29</v>
+      </c>
+      <c r="S25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="8">
+        <f>SUM(O25:S25)</f>
+        <v/>
+      </c>
+      <c r="U25" s="9">
+        <f>N25+T25</f>
+        <v/>
+      </c>
+      <c r="V25" s="7" t="n">
+        <v>2980.92</v>
+      </c>
+      <c r="W25" s="10">
+        <f>ROUND(U25-V25,2)</f>
+        <v/>
+      </c>
+      <c r="X25" s="11" t="n"/>
+      <c r="Y25" s="12" t="inlineStr">
         <is>
           <t>Comissão apurada R$ 825,38 × 2.</t>
         </is>
@@ -1811,29 +2367,56 @@
       <c r="I26" s="7" t="n">
         <v>260</v>
       </c>
-      <c r="J26" s="8">
-        <f>SUM(B26:I26)</f>
-        <v/>
+      <c r="J26" s="7" t="n">
+        <v>100</v>
       </c>
       <c r="K26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="8">
+        <f>SUM(B26:M26)</f>
+        <v/>
+      </c>
+      <c r="O26" s="7" t="n">
         <v>-260</v>
       </c>
-      <c r="L26" s="9" t="n"/>
-      <c r="M26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="8">
-        <f>SUM(K26:M26)</f>
-        <v/>
-      </c>
-      <c r="O26" s="10">
-        <f>J26+N26</f>
-        <v/>
-      </c>
-      <c r="P26" s="9" t="n"/>
-      <c r="Q26" s="11" t="inlineStr">
-        <is>
-          <t>Comissão apurada R$ 886,30 × 2.</t>
+      <c r="P26" s="7" t="n">
+        <v>-580</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="7" t="n">
+        <v>-348.72</v>
+      </c>
+      <c r="S26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="8">
+        <f>SUM(O26:S26)</f>
+        <v/>
+      </c>
+      <c r="U26" s="9">
+        <f>N26+T26</f>
+        <v/>
+      </c>
+      <c r="V26" s="7" t="n">
+        <v>2905.76</v>
+      </c>
+      <c r="W26" s="10">
+        <f>ROUND(U26-V26,2)</f>
+        <v/>
+      </c>
+      <c r="X26" s="11" t="n"/>
+      <c r="Y26" s="12" t="inlineStr">
+        <is>
+          <t>Comissão apurada R$ 886,30 × 2. Férias de 01 a 30/09/2026.</t>
         </is>
       </c>
     </row>
@@ -1867,27 +2450,54 @@
       <c r="I27" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="8">
-        <f>SUM(B27:I27)</f>
-        <v/>
+      <c r="J27" s="7" t="n">
+        <v>100</v>
       </c>
       <c r="K27" s="7" t="n">
+        <v>85.02</v>
+      </c>
+      <c r="L27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="8">
+        <f>SUM(B27:M27)</f>
+        <v/>
+      </c>
+      <c r="O27" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="L27" s="9" t="n"/>
-      <c r="M27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="8">
-        <f>SUM(K27:M27)</f>
-        <v/>
-      </c>
-      <c r="O27" s="10">
-        <f>J27+N27</f>
-        <v/>
-      </c>
-      <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="11" t="inlineStr">
+      <c r="P27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="7" t="n">
+        <v>-236.18</v>
+      </c>
+      <c r="S27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="8">
+        <f>SUM(O27:S27)</f>
+        <v/>
+      </c>
+      <c r="U27" s="9">
+        <f>N27+T27</f>
+        <v/>
+      </c>
+      <c r="V27" s="7" t="n">
+        <v>2658.33</v>
+      </c>
+      <c r="W27" s="10">
+        <f>ROUND(U27-V27,2)</f>
+        <v/>
+      </c>
+      <c r="X27" s="11" t="n"/>
+      <c r="Y27" s="12" t="inlineStr">
         <is>
           <t>Comissão apurada R$ 235,42 × 2. 40 horas extras.</t>
         </is>
@@ -1923,99 +2533,158 @@
       <c r="I28" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="8">
-        <f>SUM(B28:I28)</f>
-        <v/>
+      <c r="J28" s="7" t="n">
+        <v>100</v>
       </c>
       <c r="K28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="8">
+        <f>SUM(B28:M28)</f>
+        <v/>
+      </c>
+      <c r="O28" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="L28" s="9" t="n"/>
-      <c r="M28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="8">
-        <f>SUM(K28:M28)</f>
-        <v/>
-      </c>
-      <c r="O28" s="10">
-        <f>J28+N28</f>
-        <v/>
-      </c>
-      <c r="P28" s="9" t="n"/>
-      <c r="Q28" s="11" t="inlineStr">
+      <c r="P28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="7" t="n">
+        <v>-157.52</v>
+      </c>
+      <c r="S28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="8">
+        <f>SUM(O28:S28)</f>
+        <v/>
+      </c>
+      <c r="U28" s="9">
+        <f>N28+T28</f>
+        <v/>
+      </c>
+      <c r="V28" s="7" t="n">
+        <v>1862.94</v>
+      </c>
+      <c r="W28" s="10">
+        <f>ROUND(U28-V28,2)</f>
+        <v/>
+      </c>
+      <c r="X28" s="11" t="n"/>
+      <c r="Y28" s="12" t="inlineStr">
         <is>
           <t>Comissão apurada R$ 125,58 × 2. Atestado de 02 a 08/09 é competência de setembro.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>TOTAL TRANCOSO</t>
         </is>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="10">
         <f>SUM(B24:B28)</f>
         <v/>
       </c>
-      <c r="C29" s="13">
+      <c r="C29" s="10">
         <f>SUM(C24:C28)</f>
         <v/>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="10">
         <f>SUM(D24:D28)</f>
         <v/>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="10">
         <f>SUM(E24:E28)</f>
         <v/>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="10">
         <f>SUM(F24:F28)</f>
         <v/>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="10">
         <f>SUM(G24:G28)</f>
         <v/>
       </c>
-      <c r="H29" s="13">
+      <c r="H29" s="10">
         <f>SUM(H24:H28)</f>
         <v/>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="10">
         <f>SUM(I24:I28)</f>
         <v/>
       </c>
-      <c r="J29" s="13">
+      <c r="J29" s="10">
         <f>SUM(J24:J28)</f>
         <v/>
       </c>
-      <c r="K29" s="13">
+      <c r="K29" s="10">
         <f>SUM(K24:K28)</f>
         <v/>
       </c>
-      <c r="L29" s="13">
+      <c r="L29" s="10">
         <f>SUM(L24:L28)</f>
         <v/>
       </c>
-      <c r="M29" s="13">
+      <c r="M29" s="10">
         <f>SUM(M24:M28)</f>
         <v/>
       </c>
-      <c r="N29" s="13">
+      <c r="N29" s="10">
         <f>SUM(N24:N28)</f>
         <v/>
       </c>
-      <c r="O29" s="13">
+      <c r="O29" s="10">
         <f>SUM(O24:O28)</f>
         <v/>
       </c>
-      <c r="P29" s="13">
+      <c r="P29" s="10">
         <f>SUM(P24:P28)</f>
         <v/>
       </c>
-      <c r="Q29" s="14" t="n"/>
+      <c r="Q29" s="10">
+        <f>SUM(Q24:Q28)</f>
+        <v/>
+      </c>
+      <c r="R29" s="10">
+        <f>SUM(R24:R28)</f>
+        <v/>
+      </c>
+      <c r="S29" s="10">
+        <f>SUM(S24:S28)</f>
+        <v/>
+      </c>
+      <c r="T29" s="10">
+        <f>SUM(T24:T28)</f>
+        <v/>
+      </c>
+      <c r="U29" s="10">
+        <f>SUM(U24:U28)</f>
+        <v/>
+      </c>
+      <c r="V29" s="10">
+        <f>SUM(V24:V28)</f>
+        <v/>
+      </c>
+      <c r="W29" s="10">
+        <f>SUM(W24:W28)</f>
+        <v/>
+      </c>
+      <c r="X29" s="10">
+        <f>SUM(X24:X28)</f>
+        <v/>
+      </c>
+      <c r="Y29" s="14" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
@@ -2083,129 +2752,177 @@
         <f>P14+P22+P29</f>
         <v/>
       </c>
-      <c r="Q31" s="17" t="n"/>
+      <c r="Q31" s="16">
+        <f>Q14+Q22+Q29</f>
+        <v/>
+      </c>
+      <c r="R31" s="16">
+        <f>R14+R22+R29</f>
+        <v/>
+      </c>
+      <c r="S31" s="16">
+        <f>S14+S22+S29</f>
+        <v/>
+      </c>
+      <c r="T31" s="16">
+        <f>T14+T22+T29</f>
+        <v/>
+      </c>
+      <c r="U31" s="16">
+        <f>U14+U22+U29</f>
+        <v/>
+      </c>
+      <c r="V31" s="16">
+        <f>V14+V22+V29</f>
+        <v/>
+      </c>
+      <c r="W31" s="16">
+        <f>W14+W22+W29</f>
+        <v/>
+      </c>
+      <c r="X31" s="16">
+        <f>X14+X22+X29</f>
+        <v/>
+      </c>
+      <c r="Y31" s="17" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>O QUE AINDA NÃO ESTÁ NESTE RESUMO — precisa ser somado antes de fechar o holerite:</t>
+          <t>PONTOS EM ABERTO:</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>• INSS e IRRF de cada funcionário (cálculo da contabilidade) — por isso a última coluna é LÍQUIDO PARCIAL.</t>
+          <t>• JOEL (Arraial): a comissão de R$ 103,31 e o DSR não entraram no holerite — só saiu o salário família. Verificar folha complementar ou recibo de férias.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>• Convênio e descontos de falta do mês.</t>
+          <t>• GENECIR (Centro): comissão residual de R$ 0,62 fora do holerite.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>• A coluna ADIANTAMENTO SALARIAL / VALES está em amarelo, para preencher com o valor adiantado a cada um (em negativo). O total de descontos e o líquido se atualizam sozinhos.</t>
+          <t>• PEDRO (Centro): não consta no holerite emitido pela Betel para esta loja.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>• Prêmio cota geral e prêmio pré-vencidos, conforme a apuração de metas de cada loja.</t>
+          <t>• DSR EM DUPLICIDADE: a rubrica 420 (Repouso Remunerado) já foi calculada sobre comissão + horas extras, e a Betel ainda lançou a rubrica 057 (DSR/hora extra). São R$ 51,01 do EDEY, R$ 46,51 da NATI, R$ 10,38 de VALÉRIA, SARA e CAMILA e R$ 85,02 do INIURLE — R$ 213,68 no total. Confirmar com a contabilidade.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>• A coluna FÉRIAS PAGAS À PARTE é só lembrete para o contas a pagar: recibo de férias pago fora do holerite, NÃO entra no líquido. Em agosto: JOEL (Arraial, férias de 01 a 31/08) e GENECIR (Centro, férias de 01 a 30/08).</t>
+          <t>• Prêmio cota geral e prêmio pré-vencidos, conforme a apuração de metas de cada loja.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
+          <t>• A coluna FÉRIAS PAGAS À PARTE é só lembrete para o contas a pagar: recibo de férias pago fora do holerite, NÃO entra no líquido. Em agosto: JOEL (Arraial, férias de 01 a 31/08) e GENECIR (Centro, férias de 01 a 30/08).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
           <t>• Diárias dos folguistas SERGIO (R$ 150,00) e ANA CELIA (R$ 100,00), na loja Centro — vão para o contas a pagar, fora do holerite.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="19" t="inlineStr"/>
-    </row>
     <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>CRITÉRIOS USADOS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="19" t="inlineStr">
-        <is>
-          <t>• DSR sobre comissão e horas extras: 5 domingos ÷ 26 dias úteis de agosto/2026 = fator 0,192307.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>• Salário-hora = salário ÷ 220. Hora extra = salário-hora × 1,5 (R$ 11,0523). Adicional noturno = salário-hora × 20% (R$ 1,4736).</t>
+          <t>• DSR sobre comissão e horas extras: 5 domingos ÷ 26 dias úteis de agosto/2026 = fator 0,192307.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>• Feriado de 15/08 trabalhado sem folga = 1 salário-dia a mais (R$ 54,03).</t>
+          <t>• Salário-hora = salário ÷ 220. Hora extra = salário-hora × 1,5 (R$ 11,0523). Adicional noturno = salário-hora × 20% (R$ 1,4736).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>• TRANCOSO paga o dobro da comissão apurada no InovaFarma; os incentivos entram pelo valor simples.</t>
+          <t>• Feriado de 15/08 trabalhado sem folga = 1 salário-dia a mais (R$ 54,03).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>• Os incentivos são adiantados em dinheiro durante o mês, por isso aparecem como provento e como desconto (ADIANT. INCENT.).</t>
+          <t>• TRANCOSO paga o dobro da comissão apurada no InovaFarma; os incentivos entram pelo valor simples.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
         <is>
+          <t>• Os incentivos são adiantados em dinheiro durante o mês e NÃO aparecem no holerite da Betel; aqui entram como provento e como desconto, sem afetar o líquido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>• Prêmios, vales, vale-transporte, INSS e IRRF foram lidos do holerite de agosto/2026 emitido pela Betel Contabilidade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
           <t>• Comissões e incentivos vêm do relatório do InovaFarma de 01/08 a 31/08/2026, extraído em 03/09/2026.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q29"/>
-  <mergeCells count="17">
-    <mergeCell ref="A44:Q44"/>
-    <mergeCell ref="A40:Q40"/>
-    <mergeCell ref="A46:Q46"/>
-    <mergeCell ref="A39:Q39"/>
-    <mergeCell ref="A34:Q34"/>
-    <mergeCell ref="A35:Q35"/>
-    <mergeCell ref="A43:Q43"/>
-    <mergeCell ref="A38:Q38"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="A41:Q41"/>
-    <mergeCell ref="A33:Q33"/>
-    <mergeCell ref="A45:Q45"/>
-    <mergeCell ref="A47:Q47"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A37:Q37"/>
-    <mergeCell ref="A36:Q36"/>
+  <autoFilter ref="A4:Y29"/>
+  <mergeCells count="19">
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A33:Y33"/>
+    <mergeCell ref="A47:Y47"/>
+    <mergeCell ref="A42:Y42"/>
+    <mergeCell ref="A35:Y35"/>
+    <mergeCell ref="A43:Y43"/>
+    <mergeCell ref="A38:Y38"/>
+    <mergeCell ref="A44:Y44"/>
+    <mergeCell ref="A40:Y40"/>
+    <mergeCell ref="A34:Y34"/>
+    <mergeCell ref="A48:Y48"/>
+    <mergeCell ref="A39:Y39"/>
+    <mergeCell ref="A49:Y49"/>
+    <mergeCell ref="A36:Y36"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A45:Y45"/>
+    <mergeCell ref="A41:Y41"/>
+    <mergeCell ref="A46:Y46"/>
+    <mergeCell ref="A37:Y37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
